--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6164-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6164-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{120C2D69-DB6B-42F0-8EB1-73B0C64F1A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E313F29-749B-4FBA-8BD5-7424DB61B338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{7082607A-90DD-4B98-B44E-26108F394030}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{10D913E8-A4A8-4AFF-8183-9ABBC1CCB8F0}"/>
   </bookViews>
   <sheets>
     <sheet name="6164-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1499,28 +1499,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD538D8-ABA5-4806-83D3-26338A75FE0B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A768B7-B433-4A53-9845-DD3C9D45BE9C}">
   <dimension ref="A1:X35"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1554,7 +1554,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1590,7 +1590,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1710,7 +1710,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>31</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>31</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>31</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="34">
         <v>2018</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="36">
         <v>2017</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="34">
         <v>2016</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="36">
         <v>2015</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="34">
         <v>2014</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="36">
         <v>2013</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="34">
         <v>2012</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="36">
         <v>2011</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="34">
         <v>2010</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="36">
         <v>2009</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="34">
         <v>2008</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="36">
         <v>2007</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="34">
         <v>2006</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>6.09</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="36">
         <v>2005</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="34">
         <v>2004</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="36">
         <v>2003</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="34">
         <v>2002</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="36">
         <v>2001</v>
       </c>
@@ -3660,7 +3660,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="34">
         <v>2000</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="36">
         <v>1999</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="34">
         <v>1998</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="36" t="s">
         <v>55</v>
       </c>
